--- a/엑셀 파일 튜토리얼/sales_report.xlsx
+++ b/엑셀 파일 튜토리얼/sales_report.xlsx
@@ -279,6 +279,21 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>월별 매출 (단위: 백만원)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
     <plotArea>
       <lineChart>
         <grouping val="standard"/>
@@ -299,9 +314,16 @@
             </a:ln>
           </spPr>
           <marker>
-            <symbol val="none"/>
+            <symbol val="circle"/>
+            <size val="6"/>
             <spPr>
+              <a:solidFill>
+                <a:srgbClr val="A50034"/>
+              </a:solidFill>
               <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="A50034"/>
+                </a:solidFill>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -316,6 +338,7 @@
               <f>'분석 결과'!$C$9:$C$20</f>
             </numRef>
           </val>
+          <smooth val="0"/>
         </ser>
         <axId val="10"/>
         <axId val="100"/>
@@ -325,9 +348,29 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0">
+                <a:solidFill>
+                  <a:srgbClr val="6B6B6B"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr sz="900" b="0">
+              <a:solidFill>
+                <a:srgbClr val="6B6B6B"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:endParaRPr>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -336,9 +379,30 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
+        <numFmt formatCode="#,##0,,&quot;M&quot;" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0">
+                <a:solidFill>
+                  <a:srgbClr val="6B6B6B"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr sz="900" b="0">
+              <a:solidFill>
+                <a:srgbClr val="6B6B6B"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:endParaRPr>
+          </a:p>
+        </txPr>
         <crossAx val="10"/>
       </valAx>
     </plotArea>
@@ -352,6 +416,21 @@
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>지역별 매출 (단위: 백만원)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
     <plotArea>
       <barChart>
         <barDir val="bar"/>
@@ -386,6 +465,32 @@
             </numRef>
           </val>
         </ser>
+        <dLbls>
+          <numFmt formatCode="#,##0,,&quot;M&quot;"/>
+          <txPr>
+            <a:bodyPr/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="800" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="6B6B6B"/>
+                  </a:solidFill>
+                  <a:latin typeface="Calibri"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr sz="800" b="0">
+                <a:solidFill>
+                  <a:srgbClr val="6B6B6B"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:endParaRPr>
+            </a:p>
+          </txPr>
+          <showLegendKey val="0"/>
+          <showVal val="1"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
+        </dLbls>
         <gapWidth val="150"/>
         <axId val="10"/>
         <axId val="100"/>
@@ -395,9 +500,29 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0">
+                <a:solidFill>
+                  <a:srgbClr val="6B6B6B"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr sz="900" b="0">
+              <a:solidFill>
+                <a:srgbClr val="6B6B6B"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:endParaRPr>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -406,9 +531,30 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
+        <numFmt formatCode="#,##0,,&quot;M&quot;" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0">
+                <a:solidFill>
+                  <a:srgbClr val="6B6B6B"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr sz="900" b="0">
+              <a:solidFill>
+                <a:srgbClr val="6B6B6B"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:endParaRPr>
+          </a:p>
+        </txPr>
         <crossAx val="10"/>
       </valAx>
     </plotArea>
@@ -427,7 +573,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6120000" cy="2880000"/>
+    <ext cx="6480000" cy="3240000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -449,7 +595,7 @@
       <row>23</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6120000" cy="2880000"/>
+    <ext cx="6480000" cy="3240000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
